--- a/Configs/GameConfig/Datas/Resources.xlsx
+++ b/Configs/GameConfig/Datas/Resources.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EntityConfig" sheetId="1" r:id="R9b6700ff069048b0"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIFormConfig" sheetId="2" r:id="R1782c4f46dca434d"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoundConfig" sheetId="3" r:id="R6d5b20fb997948f1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EntityConfig" sheetId="1" r:id="Rba61a6015eb14b2a"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIFormConfig" sheetId="2" r:id="Re92f4bd7307c400b"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SoundConfig" sheetId="3" r:id="R682c0d8fcd2d4979"/>
   </sheets>
 </workbook>
 </file>
@@ -536,7 +536,7 @@
         <v>Wukong</v>
       </c>
       <c r="D6" s="11" t="str">
-        <v>res://TheGame/Entitys/wukong_entity.tscn</v>
+        <v>res://TheGame/Entitys/Heroes/Wukong/wukong_entity.tscn</v>
       </c>
       <c r="E6" s="11" t="str">
         <v>Actor</v>
@@ -563,7 +563,7 @@
         <v>HuaguoshanMonkey</v>
       </c>
       <c r="D7" s="11" t="str">
-        <v>res://TheGame/Entitys/huaguoshan_monkey_entity.tscn</v>
+        <v>res://TheGame/Entitys/Enemies/Monsters/huaguoshan_monkey_entity.tscn</v>
       </c>
       <c r="E7" s="11" t="str">
         <v>Actor</v>
@@ -590,7 +590,7 @@
         <v>DemonMonkey</v>
       </c>
       <c r="D8" s="11" t="str">
-        <v>res://TheGame/Entitys/demon_monkey_entity.tscn</v>
+        <v>res://TheGame/Entitys/Enemies/Monsters/demon_monkey_entity.tscn</v>
       </c>
       <c r="E8" s="11" t="str">
         <v>Actor</v>
@@ -617,7 +617,7 @@
         <v>Gorilla</v>
       </c>
       <c r="D9" s="11" t="str">
-        <v>res://TheGame/Entitys/gorilla_entity.tscn</v>
+        <v>res://TheGame/Entitys/Enemies/Monsters/gorilla_entity.tscn</v>
       </c>
       <c r="E9" s="11" t="str">
         <v>Actor</v>
@@ -634,6 +634,42 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="11" t="str">
+        <v>MacaqueKing</v>
+      </c>
+      <c r="D10" s="11" t="str">
+        <v>res://TheGame/Entitys/Enemies/Bosses/zm1_02_macaque_king/macaque_king_entity.tscn</v>
+      </c>
+      <c r="E10" s="11" t="str">
+        <v>Actor</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="11" t="str">
+        <v>TamarinKing</v>
+      </c>
+      <c r="D11" s="11" t="str">
+        <v>res://TheGame/Entitys/Enemies/Bosses/zm1_03_tamarin_king/tamarin_king_entity.tscn</v>
+      </c>
+      <c r="E11" s="11" t="str">
+        <v>Actor</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -1609,6 +1645,54 @@
         <v>res://TheGame/Audios/SFX/wukong/skills/wukong_fire_demon_landing.mp3</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C23" s="13" t="str">
+        <v>SettlementVictory</v>
+      </c>
+      <c r="D23" s="13" t="str">
+        <v>挑战成功音乐</v>
+      </c>
+      <c r="E23" s="13" t="str">
+        <v>结算阶段替换本关音乐，由 GGF Music 播放</v>
+      </c>
+      <c r="F23" s="13" t="str">
+        <v>13_Game_Victory.mp3</v>
+      </c>
+      <c r="G23" s="13" t="str">
+        <v>Music</v>
+      </c>
+      <c r="H23" s="13" t="str">
+        <v>res://TheGame/Audios/Music/settlement_victory.mp3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="C24" s="13" t="str">
+        <v>SettlementDefeat</v>
+      </c>
+      <c r="D24" s="13" t="str">
+        <v>挑战失败音乐</v>
+      </c>
+      <c r="E24" s="13" t="str">
+        <v>结算阶段替换本关音乐，由 GGF Music 播放</v>
+      </c>
+      <c r="F24" s="13" t="str">
+        <v>12_over.mp3</v>
+      </c>
+      <c r="G24" s="13" t="str">
+        <v>Music</v>
+      </c>
+      <c r="H24" s="13" t="str">
+        <v>res://TheGame/Audios/Music/settlement_defeat.mp3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
